--- a/resources/templates/standard/F2100-05.xlsx
+++ b/resources/templates/standard/F2100-05.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>공정면허 이론 평가서 (갑지)</t>
   </si>
@@ -654,12 +657,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -682,15 +687,15 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -765,7 +770,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -783,14 +788,14 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
       <c r="V4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
@@ -805,7 +810,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -823,14 +828,14 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
@@ -845,14 +850,14 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
@@ -865,14 +870,14 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
@@ -887,7 +892,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -915,19 +920,19 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB7" s="12"/>
       <c r="AC7" s="12"/>
       <c r="AD7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE7" s="12"/>
       <c r="AF7" s="12"/>
     </row>
     <row r="8" ht="23.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="13" ht="23.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1271,7 +1276,7 @@
     </row>
     <row r="18" ht="23.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -1443,7 +1448,7 @@
     </row>
     <row r="23" ht="23.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -1615,7 +1620,7 @@
     </row>
     <row r="28" ht="23.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -1791,7 +1796,7 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
@@ -1891,7 +1896,7 @@
     </row>
     <row r="36" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1919,19 +1924,19 @@
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
       <c r="AA36" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB36" s="12"/>
       <c r="AC36" s="12"/>
       <c r="AD36" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE36" s="12"/>
       <c r="AF36" s="12"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -2103,7 +2108,7 @@
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -2275,7 +2280,7 @@
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -2447,7 +2452,7 @@
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -2619,7 +2624,7 @@
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
